--- a/artfynd/A 11312-2020 artfynd.xlsx
+++ b/artfynd/A 11312-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 11312-2020 artfynd.xlsx
+++ b/artfynd/A 11312-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,272 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125660136</v>
+      </c>
+      <c r="B3" t="n">
+        <v>109082</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stuvvik, Boh</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>328832</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6459641</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ytterslänt på norra sidan om vägen.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125660063</v>
+      </c>
+      <c r="B4" t="n">
+        <v>109082</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stuvvik, väg O668, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>328877</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6459672</v>
+      </c>
+      <c r="S4" t="n">
+        <v>75</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hjärtum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Innerslänt på norra sidan om vägen.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elvira Ljungberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11312-2020 artfynd.xlsx
+++ b/artfynd/A 11312-2020 artfynd.xlsx
@@ -792,15 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125660136</v>
+        <v>125660063</v>
       </c>
       <c r="B3" t="n">
-        <v>109082</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109137</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,17 +835,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Stuvvik, Boh</t>
+          <t>Stuvvik, väg O668, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>328832</v>
+        <v>328877</v>
       </c>
       <c r="R3" t="n">
-        <v>6459641</v>
+        <v>6459672</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>75</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,12 +884,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ytterslänt på norra sidan om vägen.</t>
+          <t>Innerslänt på norra sidan om vägen.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,15 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125660063</v>
+        <v>125660136</v>
       </c>
       <c r="B4" t="n">
-        <v>109082</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>109137</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,17 +963,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stuvvik, väg O668, Boh</t>
+          <t>Stuvvik, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>328877</v>
+        <v>328832</v>
       </c>
       <c r="R4" t="n">
-        <v>6459672</v>
+        <v>6459641</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1022,12 +1012,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Innerslänt på norra sidan om vägen.</t>
+          <t>Ytterslänt på norra sidan om vägen.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 11312-2020 artfynd.xlsx
+++ b/artfynd/A 11312-2020 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>125660063</v>
       </c>
       <c r="B3" t="n">
-        <v>109137</v>
+        <v>109144</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>125660136</v>
       </c>
       <c r="B4" t="n">
-        <v>109137</v>
+        <v>109144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11312-2020 artfynd.xlsx
+++ b/artfynd/A 11312-2020 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>125660063</v>
       </c>
       <c r="B3" t="n">
-        <v>109144</v>
+        <v>109147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>125660136</v>
       </c>
       <c r="B4" t="n">
-        <v>109144</v>
+        <v>109147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11312-2020 artfynd.xlsx
+++ b/artfynd/A 11312-2020 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>125660063</v>
       </c>
       <c r="B3" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>125660136</v>
       </c>
       <c r="B4" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11312-2020 artfynd.xlsx
+++ b/artfynd/A 11312-2020 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>125660063</v>
       </c>
       <c r="B3" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>125660136</v>
       </c>
       <c r="B4" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11312-2020 artfynd.xlsx
+++ b/artfynd/A 11312-2020 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>125660063</v>
       </c>
       <c r="B3" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>125660136</v>
       </c>
       <c r="B4" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11312-2020 artfynd.xlsx
+++ b/artfynd/A 11312-2020 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>125660063</v>
       </c>
       <c r="B3" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>125660136</v>
       </c>
       <c r="B4" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11312-2020 artfynd.xlsx
+++ b/artfynd/A 11312-2020 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>125660063</v>
       </c>
       <c r="B3" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>125660136</v>
       </c>
       <c r="B4" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 11312-2020 artfynd.xlsx
+++ b/artfynd/A 11312-2020 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>125660063</v>
       </c>
       <c r="B3" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>125660136</v>
       </c>
       <c r="B4" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
